--- a/outputs/operacional/auditoria/Acionabilidade_Produtor.xlsx
+++ b/outputs/operacional/auditoria/Acionabilidade_Produtor.xlsx
@@ -11,8 +11,8 @@
     <sheet name="2_Lastro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_Agregado'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_Lastro'!$A$1:$G$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_Agregado'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_Lastro'!$A$1:$G$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,11 +97,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,10 +468,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -532,36 +532,160 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -572,10 +696,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -585,37 +709,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>PRODUTOR</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>CPF_LIMPO</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>TEM_TELEFONE</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>TEM_EMAIL</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>ACEITA_EMAIL</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>CONTATAVEL</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>EMAIL_ACIONAVEL</t>
         </is>
@@ -624,66 +748,66 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>64240082547</t>
+          <t>59831244129</t>
         </is>
       </c>
       <c r="C2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>07432927129</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="b">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>83473597746</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>03070534578</t>
+          <t>14429444019</t>
         </is>
       </c>
       <c r="C4" s="2" t="b">
@@ -703,41 +827,41 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>39103717058</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="b">
-        <v>1</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>02843959953</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>25462914865</t>
+          <t>17535560932</t>
         </is>
       </c>
       <c r="C6" s="2" t="b">
@@ -747,51 +871,51 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>48640155778</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="b">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>40321153550</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04091570184</t>
+          <t>79968460810</t>
         </is>
       </c>
       <c r="C8" s="2" t="b">
@@ -801,51 +925,51 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>24056829962</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="b">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>15313636317</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>54522675289</t>
+          <t>27570596401</t>
         </is>
       </c>
       <c r="C10" s="2" t="b">
@@ -865,41 +989,41 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>27238046827</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="b">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>07596599920</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>42626551104</t>
+          <t>66383615171</t>
         </is>
       </c>
       <c r="C12" s="2" t="b">
@@ -909,51 +1033,51 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>35158807053</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="b">
-        <v>0</v>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>54451895202</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>54544432830</t>
+          <t>23884969653</t>
         </is>
       </c>
       <c r="C14" s="2" t="b">
@@ -973,41 +1097,41 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>43280634615</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="b">
-        <v>1</v>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>64842294057</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>42843479552</t>
+          <t>62713611155</t>
         </is>
       </c>
       <c r="C16" s="2" t="b">
@@ -1027,41 +1151,41 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>28685289755</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="b">
-        <v>0</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>42579913662</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>68486661889</t>
+          <t>71902294131</t>
         </is>
       </c>
       <c r="C18" s="2" t="b">
@@ -1081,41 +1205,41 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>89994043898</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="b">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>75326973112</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>42622189092</t>
+          <t>89137189490</t>
         </is>
       </c>
       <c r="C20" s="2" t="b">
@@ -1125,51 +1249,51 @@
         <v>1</v>
       </c>
       <c r="E20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>43757584419</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="4" t="b">
-        <v>1</v>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>29218515691</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>57366096569</t>
+          <t>02278469973</t>
         </is>
       </c>
       <c r="C22" s="2" t="b">
@@ -1189,95 +1313,95 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>18449892665</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4" t="b">
-        <v>0</v>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>01398373540</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14590099217</t>
+          <t>96561014388</t>
         </is>
       </c>
       <c r="C24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>56083318195</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" s="4" t="b">
-        <v>0</v>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>57662702895</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>55231491357</t>
+          <t>75869261796</t>
         </is>
       </c>
       <c r="C26" s="2" t="b">
@@ -1287,51 +1411,51 @@
         <v>1</v>
       </c>
       <c r="E26" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>27111161528</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="b">
-        <v>1</v>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>64710276773</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>83473597746</t>
+          <t>13875927125</t>
         </is>
       </c>
       <c r="C28" s="2" t="b">
@@ -1341,51 +1465,51 @@
         <v>1</v>
       </c>
       <c r="E28" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>77418625652</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="b">
-        <v>1</v>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>56083318195</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>13433200379</t>
+          <t>71732030937</t>
         </is>
       </c>
       <c r="C30" s="2" t="b">
@@ -1395,51 +1519,51 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>17187026217</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="b">
-        <v>1</v>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>35031365024</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>13836702410</t>
+          <t>12499856984</t>
         </is>
       </c>
       <c r="C32" s="2" t="b">
@@ -1449,51 +1573,51 @@
         <v>1</v>
       </c>
       <c r="E32" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>80841241182</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="b">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>87653269097</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>41395376724</t>
+          <t>59255562588</t>
         </is>
       </c>
       <c r="C34" s="2" t="b">
@@ -1503,51 +1627,51 @@
         <v>1</v>
       </c>
       <c r="E34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>57924991251</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="b">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>17187026217</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>81273585730</t>
+          <t>85524140602</t>
         </is>
       </c>
       <c r="C36" s="2" t="b">
@@ -1557,51 +1681,51 @@
         <v>1</v>
       </c>
       <c r="E36" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>80940244550</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4" t="b">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>56342160733</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>68011280598</t>
+          <t>61847870050</t>
         </is>
       </c>
       <c r="C38" s="2" t="b">
@@ -1611,51 +1735,51 @@
         <v>1</v>
       </c>
       <c r="E38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>05129276637</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4" t="b">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>51256746807</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>78774701687</t>
+          <t>55449647598</t>
         </is>
       </c>
       <c r="C40" s="2" t="b">
@@ -1675,41 +1799,41 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>25534192832</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4" t="b">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>22535841438</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>75003691559</t>
+          <t>93990916998</t>
         </is>
       </c>
       <c r="C42" s="2" t="b">
@@ -1719,51 +1843,51 @@
         <v>1</v>
       </c>
       <c r="E42" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>15890429025</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4" t="b">
-        <v>0</v>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>18102203173</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>52677223306</t>
+          <t>49588039551</t>
         </is>
       </c>
       <c r="C44" s="2" t="b">
@@ -1773,51 +1897,51 @@
         <v>1</v>
       </c>
       <c r="E44" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>85642059304</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4" t="b">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>22820055778</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>47284639208</t>
         </is>
       </c>
       <c r="C46" s="2" t="b">
@@ -1837,41 +1961,41 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>13858542493</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4" t="b">
-        <v>0</v>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>31752071678</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>89026012796</t>
+          <t>60466183982</t>
         </is>
       </c>
       <c r="C48" s="2" t="b">
@@ -1881,51 +2005,51 @@
         <v>1</v>
       </c>
       <c r="E48" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>26860259222</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="b">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>26368970283</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>58514936899</t>
+          <t>01372151070</t>
         </is>
       </c>
       <c r="C50" s="2" t="b">
@@ -1935,51 +2059,51 @@
         <v>1</v>
       </c>
       <c r="E50" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>47284639208</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="4" t="b">
-        <v>0</v>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>32677360260</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12499856984</t>
+          <t>93157279194</t>
         </is>
       </c>
       <c r="C52" s="2" t="b">
@@ -1999,41 +2123,41 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>84511544796</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F53" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G53" s="4" t="b">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>87258874495</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>42843479552</t>
         </is>
       </c>
       <c r="C54" s="2" t="b">
@@ -2053,41 +2177,41 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>52056647423</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" s="4" t="b">
-        <v>1</v>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>04341651827</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>08589944171</t>
+          <t>55460158517</t>
         </is>
       </c>
       <c r="C56" s="2" t="b">
@@ -2097,51 +2221,51 @@
         <v>1</v>
       </c>
       <c r="E56" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>80392827229</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="b">
-        <v>0</v>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>04556110022</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>24051477053</t>
+          <t>09859317461</t>
         </is>
       </c>
       <c r="C58" s="2" t="b">
@@ -2161,41 +2285,41 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>37562890028</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" s="4" t="b">
-        <v>0</v>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>65094801413</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>57027937145</t>
+          <t>11435190669</t>
         </is>
       </c>
       <c r="C60" s="2" t="b">
@@ -2205,51 +2329,51 @@
         <v>1</v>
       </c>
       <c r="E60" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>62244472126</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D61" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G61" s="4" t="b">
-        <v>0</v>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>99552717744</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>87258874495</t>
+          <t>28685289755</t>
         </is>
       </c>
       <c r="C62" s="2" t="b">
@@ -2259,51 +2383,51 @@
         <v>1</v>
       </c>
       <c r="E62" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>38657191826</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D63" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" s="4" t="b">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>11266912153</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>71657262849</t>
+          <t>77418625652</t>
         </is>
       </c>
       <c r="C64" s="2" t="b">
@@ -2323,41 +2447,41 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>70335211039</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="4" t="b">
-        <v>0</v>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>39385258001</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>42836440892</t>
+          <t>08993588916</t>
         </is>
       </c>
       <c r="C66" s="2" t="b">
@@ -2367,51 +2491,51 @@
         <v>1</v>
       </c>
       <c r="E66" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>74783667428</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="4" t="b">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>54019380262</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>75901751863</t>
+          <t>32898614341</t>
         </is>
       </c>
       <c r="C68" s="2" t="b">
@@ -2421,51 +2545,51 @@
         <v>1</v>
       </c>
       <c r="E68" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G68" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>15313636317</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D69" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G69" s="4" t="b">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>37124065965</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>78292216995</t>
+          <t>13736785082</t>
         </is>
       </c>
       <c r="C70" s="2" t="b">
@@ -2475,51 +2599,51 @@
         <v>1</v>
       </c>
       <c r="E70" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G70" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>54868740345</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D71" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F71" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G71" s="4" t="b">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>14921643347</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>45547813767</t>
+          <t>89994043898</t>
         </is>
       </c>
       <c r="C72" s="2" t="b">
@@ -2529,51 +2653,51 @@
         <v>1</v>
       </c>
       <c r="E72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>85368663266</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D73" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G73" s="4" t="b">
-        <v>0</v>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>81845184894</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14163356588</t>
+          <t>57437489691</t>
         </is>
       </c>
       <c r="C74" s="2" t="b">
@@ -2583,51 +2707,51 @@
         <v>1</v>
       </c>
       <c r="E74" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G74" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>08740640391</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" s="4" t="b">
-        <v>1</v>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>46591166553</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>09521456232</t>
+          <t>46785445877</t>
         </is>
       </c>
       <c r="C76" s="2" t="b">
@@ -2637,51 +2761,51 @@
         <v>1</v>
       </c>
       <c r="E76" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G76" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>04633312797</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G77" s="4" t="b">
-        <v>0</v>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>77739260302</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>05415667652</t>
+          <t>24508821009</t>
         </is>
       </c>
       <c r="C78" s="2" t="b">
@@ -2701,41 +2825,41 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>03669096705</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F79" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G79" s="4" t="b">
-        <v>1</v>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>08635365419</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>49588039551</t>
+          <t>45868501429</t>
         </is>
       </c>
       <c r="C80" s="2" t="b">
@@ -2745,51 +2869,51 @@
         <v>1</v>
       </c>
       <c r="E80" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G80" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>64746872343</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D81" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G81" s="4" t="b">
-        <v>0</v>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>60843256216</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>32161107603</t>
+          <t>58842524105</t>
         </is>
       </c>
       <c r="C82" s="2" t="b">
@@ -2809,41 +2933,41 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>63942788165</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D83" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F83" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G83" s="4" t="b">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>06181753443</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>34721228160</t>
+          <t>01581449147</t>
         </is>
       </c>
       <c r="C84" s="2" t="b">
@@ -2853,51 +2977,51 @@
         <v>1</v>
       </c>
       <c r="E84" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G84" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>26204505331</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D85" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G85" s="4" t="b">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>76973577907</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D85" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>42625827390</t>
+          <t>24451076226</t>
         </is>
       </c>
       <c r="C86" s="2" t="b">
@@ -2907,51 +3031,51 @@
         <v>1</v>
       </c>
       <c r="E86" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G86" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>55394237333</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D87" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G87" s="4" t="b">
-        <v>0</v>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>30385677005</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>04727790104</t>
+          <t>58514936899</t>
         </is>
       </c>
       <c r="C88" s="2" t="b">
@@ -2961,51 +3085,51 @@
         <v>1</v>
       </c>
       <c r="E88" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G88" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>53926442209</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D89" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G89" s="4" t="b">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>77547812914</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D89" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>69308488725</t>
+          <t>19906234456</t>
         </is>
       </c>
       <c r="C90" s="2" t="b">
@@ -3015,51 +3139,51 @@
         <v>1</v>
       </c>
       <c r="E90" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G90" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>33898881671</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D91" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G91" s="4" t="b">
-        <v>0</v>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>44714627301</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>37923747407</t>
+          <t>39690784473</t>
         </is>
       </c>
       <c r="C92" s="2" t="b">
@@ -3069,51 +3193,51 @@
         <v>1</v>
       </c>
       <c r="E92" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G92" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>11908334280</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D93" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F93" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G93" s="4" t="b">
-        <v>1</v>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>01676184723</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D93" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G93" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10433218196</t>
+          <t>38663177971</t>
         </is>
       </c>
       <c r="C94" s="2" t="b">
@@ -3133,41 +3257,41 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>02278469973</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D95" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F95" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G95" s="4" t="b">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>09521456232</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>08240433504</t>
+          <t>78078235784</t>
         </is>
       </c>
       <c r="C96" s="2" t="b">
@@ -3187,41 +3311,41 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>28699041379</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D97" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F97" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G97" s="4" t="b">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>42498182992</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G97" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>07903067383</t>
+          <t>98992172233</t>
         </is>
       </c>
       <c r="C98" s="2" t="b">
@@ -3241,41 +3365,41 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>44935348740</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D99" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F99" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G99" s="4" t="b">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>63122417974</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>44270312073</t>
+          <t>71236851604</t>
         </is>
       </c>
       <c r="C100" s="2" t="b">
@@ -3285,51 +3409,51 @@
         <v>1</v>
       </c>
       <c r="E100" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G100" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>76617711592</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D101" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E101" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F101" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G101" s="4" t="b">
-        <v>1</v>
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>22901476797</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D101" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>34163894484</t>
+          <t>99042102027</t>
         </is>
       </c>
       <c r="C102" s="2" t="b">
@@ -3349,41 +3473,41 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>91463031617</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D103" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E103" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F103" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G103" s="4" t="b">
-        <v>1</v>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>18835523124</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>18233984546</t>
+          <t>37693898331</t>
         </is>
       </c>
       <c r="C104" s="2" t="b">
@@ -3393,51 +3517,51 @@
         <v>1</v>
       </c>
       <c r="E104" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G104" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>57662702895</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D105" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E105" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F105" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G105" s="4" t="b">
-        <v>1</v>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>04091570184</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D105" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>65307450544</t>
+          <t>69340608835</t>
         </is>
       </c>
       <c r="C106" s="2" t="b">
@@ -3457,95 +3581,95 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>22961201836</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D107" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E107" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G107" s="4" t="b">
-        <v>1</v>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>87719065940</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>82974255136</t>
+          <t>25546659051</t>
         </is>
       </c>
       <c r="C108" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>98253092511</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D109" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E109" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F109" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G109" s="4" t="b">
-        <v>0</v>
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>78291146786</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>09435334485</t>
+          <t>80940244550</t>
         </is>
       </c>
       <c r="C110" s="2" t="b">
@@ -3565,41 +3689,41 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>19906234456</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D111" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E111" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F111" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G111" s="4" t="b">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>51583281826</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>51713395962</t>
+          <t>52677223306</t>
         </is>
       </c>
       <c r="C112" s="2" t="b">
@@ -3609,51 +3733,51 @@
         <v>1</v>
       </c>
       <c r="E112" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G112" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>46187234601</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D113" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E113" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F113" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G113" s="4" t="b">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>90340438427</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D113" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F113" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>38663177971</t>
+          <t>24593344196</t>
         </is>
       </c>
       <c r="C114" s="2" t="b">
@@ -3663,51 +3787,51 @@
         <v>1</v>
       </c>
       <c r="E114" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G114" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>64710276773</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D115" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E115" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G115" s="4" t="b">
-        <v>0</v>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>15451680876</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>54451895202</t>
+          <t>22499982795</t>
         </is>
       </c>
       <c r="C116" s="2" t="b">
@@ -3717,51 +3841,51 @@
         <v>1</v>
       </c>
       <c r="E116" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G116" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>49947174648</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D117" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E117" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F117" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G117" s="4" t="b">
-        <v>0</v>
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>88615335554</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>68793741608</t>
+          <t>71422410988</t>
         </is>
       </c>
       <c r="C118" s="2" t="b">
@@ -3781,41 +3905,41 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>61595148465</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D119" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E119" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F119" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G119" s="4" t="b">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>97252175250</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E119" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>91965701329</t>
+          <t>86693465472</t>
         </is>
       </c>
       <c r="C120" s="2" t="b">
@@ -3835,41 +3959,41 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>39660558303</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D121" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E121" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F121" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G121" s="4" t="b">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>13433200379</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G121" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>77739260302</t>
+          <t>83388487920</t>
         </is>
       </c>
       <c r="C122" s="2" t="b">
@@ -3889,41 +4013,41 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>43805719838</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D123" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E123" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F123" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G123" s="4" t="b">
-        <v>1</v>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>78161849593</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>46287334270</t>
+          <t>67808562718</t>
         </is>
       </c>
       <c r="C124" s="2" t="b">
@@ -3943,41 +4067,41 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>35290422842</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D125" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F125" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G125" s="4" t="b">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>63745458929</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G125" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>96627828274</t>
+          <t>37996507527</t>
         </is>
       </c>
       <c r="C126" s="2" t="b">
@@ -3997,41 +4121,41 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>09805009788</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D127" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E127" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F127" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G127" s="4" t="b">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>26984858333</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G127" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>81845184894</t>
+          <t>59916247314</t>
         </is>
       </c>
       <c r="C128" s="2" t="b">
@@ -4041,51 +4165,51 @@
         <v>1</v>
       </c>
       <c r="E128" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G128" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>90604805892</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D129" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E129" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F129" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G129" s="4" t="b">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>74993097289</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D129" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G129" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>06724004991</t>
         </is>
       </c>
       <c r="C130" s="2" t="b">
@@ -4105,41 +4229,41 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>64794738646</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D131" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E131" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F131" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G131" s="4" t="b">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>50375899757</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G131" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>05891135290</t>
+          <t>08589944171</t>
         </is>
       </c>
       <c r="C132" s="2" t="b">
@@ -4159,41 +4283,41 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>62003424420</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D133" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E133" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F133" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G133" s="4" t="b">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>37562890028</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E133" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G133" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>44144885015</t>
+          <t>91630097925</t>
         </is>
       </c>
       <c r="C134" s="2" t="b">
@@ -4203,51 +4327,51 @@
         <v>1</v>
       </c>
       <c r="E134" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G134" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>40640909743</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D135" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E135" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F135" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G135" s="4" t="b">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>68486661889</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E135" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G135" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>99880817703</t>
+          <t>51820377889</t>
         </is>
       </c>
       <c r="C136" s="2" t="b">
@@ -4257,105 +4381,105 @@
         <v>1</v>
       </c>
       <c r="E136" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G136" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>98616229991</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D137" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E137" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F137" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G137" s="4" t="b">
-        <v>1</v>
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>48640155778</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E137" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G137" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>85681193978</t>
+          <t>27238046827</t>
         </is>
       </c>
       <c r="C138" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>40084271094</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D139" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E139" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F139" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G139" s="4" t="b">
-        <v>0</v>
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>86101581995</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G139" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>36403761379</t>
+          <t>67883171210</t>
         </is>
       </c>
       <c r="C140" s="2" t="b">
@@ -4375,41 +4499,41 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>50613878293</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D141" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E141" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F141" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G141" s="4" t="b">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>65766156545</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G141" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>81814124782</t>
+          <t>49972787558</t>
         </is>
       </c>
       <c r="C142" s="2" t="b">
@@ -4419,51 +4543,51 @@
         <v>1</v>
       </c>
       <c r="E142" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G142" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>20812191361</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D143" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E143" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F143" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G143" s="4" t="b">
-        <v>0</v>
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>37923747407</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G143" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>27128639174</t>
+          <t>08613171274</t>
         </is>
       </c>
       <c r="C144" s="2" t="b">
@@ -4473,51 +4597,51 @@
         <v>1</v>
       </c>
       <c r="E144" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G144" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>76365564729</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D145" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E145" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F145" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G145" s="4" t="b">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>28168505423</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G145" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>06706540515</t>
+          <t>38657191826</t>
         </is>
       </c>
       <c r="C146" s="2" t="b">
@@ -4537,41 +4661,41 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>54788728743</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D147" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E147" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F147" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G147" s="4" t="b">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>61581487696</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G147" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>39878015739</t>
+          <t>44270312073</t>
         </is>
       </c>
       <c r="C148" s="2" t="b">
@@ -4581,51 +4705,51 @@
         <v>1</v>
       </c>
       <c r="E148" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G148" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>04899642353</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D149" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E149" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F149" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G149" s="4" t="b">
-        <v>1</v>
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>68414593327</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E149" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G149" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>02786814473</t>
+          <t>88608680347</t>
         </is>
       </c>
       <c r="C150" s="2" t="b">
@@ -4645,41 +4769,41 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>48728299796</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D151" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E151" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F151" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G151" s="4" t="b">
-        <v>1</v>
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>93333468007</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D151" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E151" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F151" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G151" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>25699611253</t>
+          <t>96631931491</t>
         </is>
       </c>
       <c r="C152" s="2" t="b">
@@ -4689,105 +4813,105 @@
         <v>1</v>
       </c>
       <c r="E152" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G152" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>54353462475</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D153" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E153" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F153" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G153" s="4" t="b">
-        <v>1</v>
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>78232983248</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E153" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G153" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>71434558122</t>
+          <t>51432191430</t>
         </is>
       </c>
       <c r="C154" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F154" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>11266912153</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D155" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E155" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F155" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G155" s="4" t="b">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>69804204394</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G155" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>46688937346</t>
+          <t>92750373145</t>
         </is>
       </c>
       <c r="C156" s="2" t="b">
@@ -4807,41 +4931,41 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>59059929378</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D157" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E157" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F157" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G157" s="4" t="b">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>79827080869</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G157" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>21495870207</t>
+          <t>96881435368</t>
         </is>
       </c>
       <c r="C158" s="2" t="b">
@@ -4851,51 +4975,51 @@
         <v>1</v>
       </c>
       <c r="E158" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G158" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>51939828073</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D159" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E159" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F159" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G159" s="4" t="b">
-        <v>1</v>
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>18785191088</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E159" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G159" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>15274205493</t>
+          <t>42701039308</t>
         </is>
       </c>
       <c r="C160" s="2" t="b">
@@ -4915,41 +5039,41 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>26011939103</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D161" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E161" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F161" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G161" s="4" t="b">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>49947174648</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D161" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E161" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F161" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G161" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>65375564641</t>
+          <t>77584161692</t>
         </is>
       </c>
       <c r="C162" s="2" t="b">
@@ -4969,41 +5093,41 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>16400524278</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D163" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E163" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F163" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G163" s="4" t="b">
-        <v>1</v>
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>54522675289</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D163" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E163" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F163" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G163" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>39690784473</t>
+          <t>93305172897</t>
         </is>
       </c>
       <c r="C164" s="2" t="b">
@@ -5013,51 +5137,51 @@
         <v>1</v>
       </c>
       <c r="E164" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G164" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>96520744666</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D165" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E165" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F165" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G165" s="4" t="b">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>20417929111</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G165" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>50375899757</t>
+          <t>66978480184</t>
         </is>
       </c>
       <c r="C166" s="2" t="b">
@@ -5067,51 +5191,51 @@
         <v>1</v>
       </c>
       <c r="E166" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G166" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>17839084700</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D167" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E167" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F167" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G167" s="4" t="b">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>70805310033</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D167" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E167" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F167" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G167" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>63122417974</t>
+          <t>33173936385</t>
         </is>
       </c>
       <c r="C168" s="2" t="b">
@@ -5131,41 +5255,41 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>20644742123</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D169" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E169" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F169" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G169" s="4" t="b">
-        <v>1</v>
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>84902770384</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D169" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E169" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G169" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>85474929751</t>
+          <t>06356512694</t>
         </is>
       </c>
       <c r="C170" s="2" t="b">
@@ -5175,51 +5299,51 @@
         <v>1</v>
       </c>
       <c r="E170" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G170" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>22901476797</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D171" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E171" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F171" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G171" s="4" t="b">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>63840666580</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D171" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E171" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F171" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G171" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>25381793355</t>
+          <t>57905528183</t>
         </is>
       </c>
       <c r="C172" s="2" t="b">
@@ -5239,41 +5363,41 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>45868501429</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D173" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E173" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F173" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G173" s="4" t="b">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>36403761379</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D173" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E173" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F173" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G173" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>47132475469</t>
+          <t>03669096705</t>
         </is>
       </c>
       <c r="C174" s="2" t="b">
@@ -5283,51 +5407,51 @@
         <v>1</v>
       </c>
       <c r="E174" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G174" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>35569092755</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D175" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E175" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F175" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G175" s="4" t="b">
-        <v>0</v>
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>91846386557</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D175" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E175" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F175" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G175" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>34125286692</t>
+          <t>74034471349</t>
         </is>
       </c>
       <c r="C176" s="2" t="b">
@@ -5337,51 +5461,51 @@
         <v>1</v>
       </c>
       <c r="E176" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G176" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>32898614341</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D177" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E177" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F177" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G177" s="4" t="b">
-        <v>1</v>
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>02726149331</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D177" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E177" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F177" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G177" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>19148564679</t>
+          <t>80841241182</t>
         </is>
       </c>
       <c r="C178" s="2" t="b">
@@ -5401,41 +5525,41 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>02771670145</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D179" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E179" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F179" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G179" s="4" t="b">
-        <v>0</v>
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>56475705120</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D179" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E179" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F179" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G179" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>69378547772</t>
+          <t>55794155216</t>
         </is>
       </c>
       <c r="C180" s="2" t="b">
@@ -5455,41 +5579,41 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>19656523413</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D181" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E181" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F181" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G181" s="4" t="b">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Bruno Corretor</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>75304637454</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D181" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E181" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F181" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G181" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>50648909010</t>
+          <t>31952058527</t>
         </is>
       </c>
       <c r="C182" s="2" t="b">
@@ -5509,41 +5633,41 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>99758172461</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D183" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E183" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F183" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G183" s="4" t="b">
-        <v>1</v>
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>20616329451</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D183" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E183" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F183" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G183" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>75304637454</t>
+          <t>96499091334</t>
         </is>
       </c>
       <c r="C184" s="2" t="b">
@@ -5563,41 +5687,41 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>82586736226</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D185" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E185" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F185" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G185" s="4" t="b">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>54788728743</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G185" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>47859696915</t>
+          <t>47411249035</t>
         </is>
       </c>
       <c r="C186" s="2" t="b">
@@ -5617,41 +5741,41 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>51509398343</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D187" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E187" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F187" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G187" s="4" t="b">
-        <v>0</v>
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>Ana Vendas</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>36815798123</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G187" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>13875927125</t>
+          <t>81273585730</t>
         </is>
       </c>
       <c r="C188" s="2" t="b">
@@ -5661,51 +5785,51 @@
         <v>1</v>
       </c>
       <c r="E188" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G188" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>12679692786</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D189" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E189" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F189" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G189" s="4" t="b">
-        <v>1</v>
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>39382761539</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D189" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E189" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G189" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>57332214188</t>
+          <t>20812191361</t>
         </is>
       </c>
       <c r="C190" s="2" t="b">
@@ -5715,51 +5839,51 @@
         <v>1</v>
       </c>
       <c r="E190" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" s="2" t="b">
         <v>1</v>
       </c>
       <c r="G190" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>86753396360</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D191" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E191" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F191" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G191" s="4" t="b">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>64746872343</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D191" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E191" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F191" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G191" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>22656766182</t>
+          <t>86652404157</t>
         </is>
       </c>
       <c r="C192" s="2" t="b">
@@ -5778,62 +5902,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>59916247314</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D193" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E193" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F193" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G193" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>52064361103</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D194" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E194" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F194" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G194" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G194"/>
+  <autoFilter ref="A1:G192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>